--- a/KIT_EMBALAJE_TODOS.xlsx
+++ b/KIT_EMBALAJE_TODOS.xlsx
@@ -1,26 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officesfg.sharepoint.com/sites/DivisionIndustrial/Documentos compartidos/Planta Malloa/Control Producción/TEMPORADA 2023-2024/TEMPORADA 25-26/PLANIFICACIÓN/TRABAJO INVIERNO26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E675AC9B-BB29-BD4F-9357-F53A5F025B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2036" documentId="8_{0A0E6D88-C993-4BE9-B521-F3C2595D2C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C867E7-DA52-4D16-8594-A89CF5FF8156}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CEREZA 2026" sheetId="1" r:id="rId1"/>
     <sheet name="NARANJA 2026" sheetId="2" r:id="rId2"/>
+    <sheet name="CHERRY PLUM" sheetId="3" r:id="rId3"/>
+    <sheet name="CIRUELAS" sheetId="4" r:id="rId4"/>
+    <sheet name="DURAZNO" sheetId="5" r:id="rId5"/>
+    <sheet name="NECTARIN" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CEREZA 2026'!$B$1:$G$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NARANJA 2026'!$B$1:$G$23</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="271">
   <si>
     <t>DESCRIPCION
 ENVASE</t>
@@ -460,13 +464,406 @@
   </si>
   <si>
     <t>32-56</t>
+  </si>
+  <si>
+    <t>C0546098</t>
+  </si>
+  <si>
+    <t>CASC10M</t>
+  </si>
+  <si>
+    <t>GARCES PREMIUM</t>
+  </si>
+  <si>
+    <t>DULCINEA</t>
+  </si>
+  <si>
+    <t>NORTEAMÉRICA</t>
+  </si>
+  <si>
+    <t>CASAC10M</t>
+  </si>
+  <si>
+    <t>USA-WALMART</t>
+  </si>
+  <si>
+    <t>CASC1WM</t>
+  </si>
+  <si>
+    <t>C8546123</t>
+  </si>
+  <si>
+    <t>CASB12M</t>
+  </si>
+  <si>
+    <t>NORTEAMERICA</t>
+  </si>
+  <si>
+    <t>CASAB12M</t>
+  </si>
+  <si>
+    <t>C9546123</t>
+  </si>
+  <si>
+    <t>CASB10M</t>
+  </si>
+  <si>
+    <t>CASAB10M</t>
+  </si>
+  <si>
+    <t>C9546133</t>
+  </si>
+  <si>
+    <t>CACC10M</t>
+  </si>
+  <si>
+    <t>COSTCO USA</t>
+  </si>
+  <si>
+    <t>CACAC10M</t>
+  </si>
+  <si>
+    <t>CASAC1TM</t>
+  </si>
+  <si>
+    <t>COSTCO TAIWAN</t>
+  </si>
+  <si>
+    <t>FRACCIONADO</t>
+  </si>
+  <si>
+    <t>P0935140</t>
+  </si>
+  <si>
+    <t>CASGMM</t>
+  </si>
+  <si>
+    <t>CASGRM</t>
+  </si>
+  <si>
+    <t>EXTREMO SUR</t>
+  </si>
+  <si>
+    <t>C0534125</t>
+  </si>
+  <si>
+    <t>C6546098</t>
+  </si>
+  <si>
+    <t>CACGRM</t>
+  </si>
+  <si>
+    <t>CASAGRA</t>
+  </si>
+  <si>
+    <t>CASAFTM</t>
+  </si>
+  <si>
+    <t>CAFPAPM</t>
+  </si>
+  <si>
+    <t>CASFTM</t>
+  </si>
+  <si>
+    <t>CASAGMM</t>
+  </si>
+  <si>
+    <t>CAFPPM</t>
+  </si>
+  <si>
+    <t>GRANEL</t>
+  </si>
+  <si>
+    <t>C0735133</t>
+  </si>
+  <si>
+    <t>CAS2BE</t>
+  </si>
+  <si>
+    <t>CAL2BE</t>
+  </si>
+  <si>
+    <t>CAH2BE</t>
+  </si>
+  <si>
+    <t>CAPC10</t>
+  </si>
+  <si>
+    <t>CAHA2BE</t>
+  </si>
+  <si>
+    <t>CALC22</t>
+  </si>
+  <si>
+    <t>C0735152</t>
+  </si>
+  <si>
+    <t>C1246185</t>
+  </si>
+  <si>
+    <t>C1446162</t>
+  </si>
+  <si>
+    <t>CAPB10</t>
+  </si>
+  <si>
+    <t>C6635133</t>
+  </si>
+  <si>
+    <t>CAP2BU</t>
+  </si>
+  <si>
+    <t>CAHT10</t>
+  </si>
+  <si>
+    <t>C9846123</t>
+  </si>
+  <si>
+    <t>CAPA2BW</t>
+  </si>
+  <si>
+    <t>CAP2BW</t>
+  </si>
+  <si>
+    <t>C1546178</t>
+  </si>
+  <si>
+    <t>CABPB9</t>
+  </si>
+  <si>
+    <t>SAMS</t>
+  </si>
+  <si>
+    <t>C6635152</t>
+  </si>
+  <si>
+    <t>C3535090</t>
+  </si>
+  <si>
+    <t>CAH1BE</t>
+  </si>
+  <si>
+    <t>C0935152</t>
+  </si>
+  <si>
+    <t>CALGRU</t>
+  </si>
+  <si>
+    <t>USA-CANADA</t>
+  </si>
+  <si>
+    <t>CAPGRU</t>
+  </si>
+  <si>
+    <t>CAFGRA</t>
+  </si>
+  <si>
+    <t>CAHGRL</t>
+  </si>
+  <si>
+    <t>LATINO AMERICA-RUSIA</t>
+  </si>
+  <si>
+    <t>CALGUX</t>
+  </si>
+  <si>
+    <t>CENTRO AMÉRICA</t>
+  </si>
+  <si>
+    <t>CASGRA</t>
+  </si>
+  <si>
+    <t>C0634125</t>
+  </si>
+  <si>
+    <t>CALGRE</t>
+  </si>
+  <si>
+    <t>CAHGRU</t>
+  </si>
+  <si>
+    <t>CAPAGRU</t>
+  </si>
+  <si>
+    <t>C1035152</t>
+  </si>
+  <si>
+    <t>CALGRL</t>
+  </si>
+  <si>
+    <t>LATINO AMÉRICA</t>
+  </si>
+  <si>
+    <t>CAHGRE</t>
+  </si>
+  <si>
+    <t>CAPGUX</t>
+  </si>
+  <si>
+    <t>MEXICO</t>
+  </si>
+  <si>
+    <t>CAFGRU</t>
+  </si>
+  <si>
+    <t>GARCES CANDY PLUMS</t>
+  </si>
+  <si>
+    <t>LATINOAMERICA</t>
+  </si>
+  <si>
+    <t>CAPGRL</t>
+  </si>
+  <si>
+    <t>PDF sin valor de ALTURA (base pallet 8 cajas)</t>
+  </si>
+  <si>
+    <t>CAFGRT</t>
+  </si>
+  <si>
+    <t>LO MISMO</t>
+  </si>
+  <si>
+    <t>CAPGUL</t>
+  </si>
+  <si>
+    <t>LAT.AMERICA-MEXICO</t>
+  </si>
+  <si>
+    <t>P0935150</t>
+  </si>
+  <si>
+    <t>CAPGRE</t>
+  </si>
+  <si>
+    <t>LATINO AMERICA</t>
+  </si>
+  <si>
+    <t>S/E              (HAPPY FLAVOUR)</t>
+  </si>
+  <si>
+    <t>CTA</t>
+  </si>
+  <si>
+    <t>C0835163</t>
+  </si>
+  <si>
+    <t>C1346162</t>
+  </si>
+  <si>
+    <t>CACWB9</t>
+  </si>
+  <si>
+    <t>Solo por contingencia</t>
+  </si>
+  <si>
+    <t>C0835152</t>
+  </si>
+  <si>
+    <t>CAH2BL</t>
+  </si>
+  <si>
+    <t>HOLANDA - LATINOAMÉRICA</t>
+  </si>
+  <si>
+    <t>CAHW9T</t>
+  </si>
+  <si>
+    <t>CACYB9</t>
+  </si>
+  <si>
+    <t>C7335163</t>
+  </si>
+  <si>
+    <t>C7635152</t>
+  </si>
+  <si>
+    <t>CAH2BU</t>
+  </si>
+  <si>
+    <t>PDF sin valor de altura (base pallet 8 cajas)</t>
+  </si>
+  <si>
+    <t>CAH2BW</t>
+  </si>
+  <si>
+    <t>C2534080</t>
+  </si>
+  <si>
+    <t>C5534133</t>
+  </si>
+  <si>
+    <t>C0435090</t>
+  </si>
+  <si>
+    <t>CASC10</t>
+  </si>
+  <si>
+    <t>C7635163</t>
+  </si>
+  <si>
+    <t>CAHA2BU</t>
+  </si>
+  <si>
+    <t>C1246141</t>
+  </si>
+  <si>
+    <t>CABPB6</t>
+  </si>
+  <si>
+    <t>C9846133</t>
+  </si>
+  <si>
+    <t>CAHC10</t>
+  </si>
+  <si>
+    <t>CANADA LOBLAW</t>
+  </si>
+  <si>
+    <t>C9535152</t>
+  </si>
+  <si>
+    <t>CAFGUX</t>
+  </si>
+  <si>
+    <t>Mercado sin valor en el PDF</t>
+  </si>
+  <si>
+    <t>RUSIA-LATINOAMÉRICA</t>
+  </si>
+  <si>
+    <t>P0835150</t>
+  </si>
+  <si>
+    <t>C0935163</t>
+  </si>
+  <si>
+    <t>LAT.AMERICA</t>
+  </si>
+  <si>
+    <t>LAT.AMERICA-RUMANIA</t>
+  </si>
+  <si>
+    <t>HAPPY FLAVOUR</t>
+  </si>
+  <si>
+    <t>CAFAGRA</t>
+  </si>
+  <si>
+    <t>CASGRU</t>
+  </si>
+  <si>
+    <t>PDF sin valor de MERCADO</t>
+  </si>
+  <si>
+    <t>CASGRT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +909,24 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="12">
@@ -582,7 +997,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -988,11 +1403,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1139,6 +1705,74 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1171,6 +1805,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1479,7 +2140,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="8">
+  <wetp:taskpane dockstate="right" visibility="0" width="454" row="8">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1502,18 +2163,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G151"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.0234375" style="36" customWidth="1"/>
-    <col min="3" max="3" width="11.97265625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="22.59765625" style="36" customWidth="1"/>
-    <col min="5" max="5" width="9.953125" style="36" customWidth="1"/>
-    <col min="6" max="6" width="13.98828125" style="36" customWidth="1"/>
-    <col min="7" max="7" width="14.390625" style="36" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18" style="36" customWidth="1"/>
+    <col min="3" max="3" width="12" style="36" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" style="36" customWidth="1"/>
+    <col min="5" max="5" width="10" style="36" customWidth="1"/>
+    <col min="6" max="6" width="14" style="36" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1533,8 +2194,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="74" t="s">
         <v>77</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1556,8 +2217,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="51"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="75"/>
       <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
@@ -1577,8 +2238,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="75"/>
       <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
@@ -1598,8 +2259,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="51"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="75"/>
       <c r="B5" s="11" t="s">
         <v>6</v>
       </c>
@@ -1617,8 +2278,8 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="51"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="75"/>
       <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
@@ -1638,8 +2299,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="75"/>
       <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
@@ -1659,8 +2320,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="75"/>
       <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
@@ -1680,8 +2341,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="51"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="75"/>
       <c r="B9" s="11" t="s">
         <v>6</v>
       </c>
@@ -1701,8 +2362,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="51"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="75"/>
       <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
@@ -1722,8 +2383,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="51"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="75"/>
       <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
@@ -1743,8 +2404,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="75"/>
       <c r="B12" s="11" t="s">
         <v>6</v>
       </c>
@@ -1764,8 +2425,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="51"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="75"/>
       <c r="B13" s="11" t="s">
         <v>6</v>
       </c>
@@ -1785,8 +2446,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="51"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="75"/>
       <c r="B14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1806,8 +2467,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="51"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="75"/>
       <c r="B15" s="11" t="s">
         <v>6</v>
       </c>
@@ -1827,8 +2488,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="75"/>
       <c r="B16" s="11" t="s">
         <v>6</v>
       </c>
@@ -1846,8 +2507,8 @@
       </c>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="51"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="75"/>
       <c r="B17" s="11" t="s">
         <v>6</v>
       </c>
@@ -1867,8 +2528,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="51"/>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="75"/>
       <c r="B18" s="11" t="s">
         <v>6</v>
       </c>
@@ -1888,8 +2549,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="51"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="75"/>
       <c r="B19" s="11" t="s">
         <v>6</v>
       </c>
@@ -1909,8 +2570,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="51"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="75"/>
       <c r="B20" s="11" t="s">
         <v>6</v>
       </c>
@@ -1930,8 +2591,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="51"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="75"/>
       <c r="B21" s="11" t="s">
         <v>6</v>
       </c>
@@ -1951,8 +2612,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="51"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="75"/>
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
@@ -1970,8 +2631,8 @@
       </c>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="51"/>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="75"/>
       <c r="B23" s="12" t="s">
         <v>6</v>
       </c>
@@ -1991,7 +2652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="3.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
       <c r="C24" s="6"/>
@@ -2000,8 +2661,8 @@
       <c r="F24" s="6"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="50" t="s">
+    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="74" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="18" t="s">
@@ -2023,8 +2684,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="51"/>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="75"/>
       <c r="B26" s="18" t="s">
         <v>26</v>
       </c>
@@ -2044,8 +2705,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="51"/>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75"/>
       <c r="B27" s="21" t="s">
         <v>26</v>
       </c>
@@ -2065,8 +2726,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="75"/>
       <c r="B28" s="21" t="s">
         <v>30</v>
       </c>
@@ -2086,8 +2747,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="51"/>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="75"/>
       <c r="B29" s="21" t="s">
         <v>30</v>
       </c>
@@ -2107,8 +2768,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="51"/>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="75"/>
       <c r="B30" s="21" t="s">
         <v>26</v>
       </c>
@@ -2128,8 +2789,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="51"/>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="75"/>
       <c r="B31" s="21" t="s">
         <v>26</v>
       </c>
@@ -2149,7 +2810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="3.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="5"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
@@ -2158,8 +2819,8 @@
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="50" t="s">
+    <row r="33" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="74" t="s">
         <v>48</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -2181,8 +2842,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="51"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="75"/>
       <c r="B34" s="11" t="s">
         <v>40</v>
       </c>
@@ -2202,8 +2863,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="51"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="75"/>
       <c r="B35" s="11" t="s">
         <v>37</v>
       </c>
@@ -2223,8 +2884,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="75"/>
       <c r="B36" s="11" t="s">
         <v>37</v>
       </c>
@@ -2244,8 +2905,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="51"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="75"/>
       <c r="B37" s="11" t="s">
         <v>37</v>
       </c>
@@ -2265,8 +2926,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="51"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="75"/>
       <c r="B38" s="11" t="s">
         <v>37</v>
       </c>
@@ -2286,8 +2947,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="51"/>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="75"/>
       <c r="B39" s="11" t="s">
         <v>37</v>
       </c>
@@ -2307,8 +2968,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="51"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="75"/>
       <c r="B40" s="11" t="s">
         <v>37</v>
       </c>
@@ -2328,8 +2989,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="51"/>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="75"/>
       <c r="B41" s="11" t="s">
         <v>40</v>
       </c>
@@ -2349,8 +3010,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="51"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="75"/>
       <c r="B42" s="11" t="s">
         <v>40</v>
       </c>
@@ -2370,8 +3031,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="51"/>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="75"/>
       <c r="B43" s="11" t="s">
         <v>37</v>
       </c>
@@ -2391,8 +3052,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="51"/>
+    <row r="44" spans="1:7" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="75"/>
       <c r="B44" s="12" t="s">
         <v>37</v>
       </c>
@@ -2410,7 +3071,7 @@
       </c>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="3.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="5"/>
       <c r="B45" s="23"/>
       <c r="C45" s="24"/>
@@ -2419,8 +3080,8 @@
       <c r="F45" s="24"/>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="50" t="s">
+    <row r="46" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="74" t="s">
         <v>78</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2442,8 +3103,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="51"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="75"/>
       <c r="B47" s="1" t="s">
         <v>49</v>
       </c>
@@ -2463,8 +3124,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="51"/>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="75"/>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,8 +3145,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="51"/>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="75"/>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
@@ -2505,8 +3166,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="50" t="s">
+    <row r="50" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="74" t="s">
         <v>76</v>
       </c>
       <c r="B50" s="26" t="s">
@@ -2528,8 +3189,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="51"/>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="75"/>
       <c r="B51" s="26" t="s">
         <v>55</v>
       </c>
@@ -2549,8 +3210,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="51"/>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="75"/>
       <c r="B52" s="26" t="s">
         <v>55</v>
       </c>
@@ -2570,8 +3231,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="51"/>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="75"/>
       <c r="B53" s="26" t="s">
         <v>55</v>
       </c>
@@ -2591,7 +3252,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="3.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="5"/>
       <c r="B54" s="23"/>
       <c r="C54" s="24"/>
@@ -2600,8 +3261,8 @@
       <c r="F54" s="24"/>
       <c r="G54" s="25"/>
     </row>
-    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="50" t="s">
+    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="74" t="s">
         <v>79</v>
       </c>
       <c r="B55" s="26" t="s">
@@ -2623,8 +3284,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="51"/>
+    <row r="56" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="75"/>
       <c r="B56" s="26" t="s">
         <v>59</v>
       </c>
@@ -2644,7 +3305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="13"/>
       <c r="C57" s="6"/>
@@ -2653,8 +3314,8 @@
       <c r="F57" s="6"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="52" t="s">
+    <row r="58" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="76" t="s">
         <v>90</v>
       </c>
       <c r="B58" s="33" t="s">
@@ -2676,8 +3337,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="52"/>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="76"/>
       <c r="B59" s="28" t="s">
         <v>89</v>
       </c>
@@ -2697,8 +3358,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="52"/>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="76"/>
       <c r="B60" s="28" t="s">
         <v>89</v>
       </c>
@@ -2718,8 +3379,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="52"/>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="76"/>
       <c r="B61" s="28" t="s">
         <v>89</v>
       </c>
@@ -2737,8 +3398,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="52"/>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="76"/>
       <c r="B62" s="28" t="s">
         <v>89</v>
       </c>
@@ -2756,8 +3417,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="52"/>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="76"/>
       <c r="B63" s="28" t="s">
         <v>89</v>
       </c>
@@ -2777,8 +3438,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="52"/>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="76"/>
       <c r="B64" s="28" t="s">
         <v>89</v>
       </c>
@@ -2796,8 +3457,8 @@
       </c>
       <c r="G64" s="28"/>
     </row>
-    <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="52"/>
+    <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="76"/>
       <c r="B65" s="28" t="s">
         <v>89</v>
       </c>
@@ -2817,8 +3478,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="52"/>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="76"/>
       <c r="B66" s="28" t="s">
         <v>89</v>
       </c>
@@ -2838,8 +3499,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="52"/>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="76"/>
       <c r="B67" s="28" t="s">
         <v>89</v>
       </c>
@@ -2859,8 +3520,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="52"/>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="76"/>
       <c r="B68" s="28" t="s">
         <v>89</v>
       </c>
@@ -2880,8 +3541,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="52"/>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="76"/>
       <c r="B69" s="28" t="s">
         <v>89</v>
       </c>
@@ -2901,8 +3562,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="52"/>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="76"/>
       <c r="B70" s="28" t="s">
         <v>89</v>
       </c>
@@ -2922,8 +3583,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="52"/>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="76"/>
       <c r="B71" s="28" t="s">
         <v>89</v>
       </c>
@@ -2943,8 +3604,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="52"/>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="76"/>
       <c r="B72" s="28" t="s">
         <v>89</v>
       </c>
@@ -2962,8 +3623,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="52"/>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="76"/>
       <c r="B73" s="28" t="s">
         <v>89</v>
       </c>
@@ -2983,8 +3644,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="52"/>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="76"/>
       <c r="B74" s="28" t="s">
         <v>89</v>
       </c>
@@ -3002,8 +3663,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="76"/>
       <c r="B75" s="28" t="s">
         <v>89</v>
       </c>
@@ -3023,8 +3684,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="76"/>
       <c r="B76" s="28" t="s">
         <v>89</v>
       </c>
@@ -3044,8 +3705,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="52"/>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" s="76"/>
       <c r="B77" s="28" t="s">
         <v>89</v>
       </c>
@@ -3063,8 +3724,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="52"/>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" s="76"/>
       <c r="B78" s="28" t="s">
         <v>89</v>
       </c>
@@ -3084,7 +3745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="13"/>
       <c r="C79" s="6"/>
@@ -3093,8 +3754,8 @@
       <c r="F79" s="6"/>
       <c r="G79" s="7"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="57" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="81" t="s">
         <v>94</v>
       </c>
       <c r="B80" s="28" t="s">
@@ -3116,8 +3777,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="57"/>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="81"/>
       <c r="B81" s="28" t="s">
         <v>6</v>
       </c>
@@ -3137,8 +3798,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="57"/>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" s="81"/>
       <c r="B82" s="28" t="s">
         <v>6</v>
       </c>
@@ -3156,8 +3817,8 @@
       </c>
       <c r="G82" s="28"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="57"/>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" s="81"/>
       <c r="B83" s="28" t="s">
         <v>6</v>
       </c>
@@ -3177,8 +3838,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="57"/>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" s="81"/>
       <c r="B84" s="28" t="s">
         <v>6</v>
       </c>
@@ -3198,8 +3859,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" s="81"/>
       <c r="B85" s="28" t="s">
         <v>6</v>
       </c>
@@ -3219,8 +3880,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="57"/>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" s="81"/>
       <c r="B86" s="28" t="s">
         <v>6</v>
       </c>
@@ -3240,8 +3901,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="57"/>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" s="81"/>
       <c r="B87" s="28" t="s">
         <v>6</v>
       </c>
@@ -3261,8 +3922,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="57"/>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" s="81"/>
       <c r="B88" s="28" t="s">
         <v>6</v>
       </c>
@@ -3280,8 +3941,8 @@
       </c>
       <c r="G88" s="28"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="57"/>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" s="81"/>
       <c r="B89" s="28" t="s">
         <v>6</v>
       </c>
@@ -3299,8 +3960,8 @@
       </c>
       <c r="G89" s="28"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="57"/>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" s="81"/>
       <c r="B90" s="28" t="s">
         <v>6</v>
       </c>
@@ -3320,8 +3981,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="57"/>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" s="81"/>
       <c r="B91" s="28" t="s">
         <v>6</v>
       </c>
@@ -3339,8 +4000,8 @@
       </c>
       <c r="G91" s="28"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="57"/>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" s="81"/>
       <c r="B92" s="28" t="s">
         <v>6</v>
       </c>
@@ -3360,8 +4021,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="57"/>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" s="81"/>
       <c r="B93" s="28" t="s">
         <v>6</v>
       </c>
@@ -3381,8 +4042,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="57"/>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" s="81"/>
       <c r="B94" s="28" t="s">
         <v>6</v>
       </c>
@@ -3402,8 +4063,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="57"/>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="81"/>
       <c r="B95" s="28" t="s">
         <v>6</v>
       </c>
@@ -3423,8 +4084,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96" s="57"/>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" s="81"/>
       <c r="B96" s="28" t="s">
         <v>6</v>
       </c>
@@ -3442,8 +4103,8 @@
       </c>
       <c r="G96" s="28"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" s="57"/>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97" s="81"/>
       <c r="B97" s="28" t="s">
         <v>6</v>
       </c>
@@ -3463,8 +4124,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" s="57"/>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98" s="81"/>
       <c r="B98" s="28" t="s">
         <v>6</v>
       </c>
@@ -3482,8 +4143,8 @@
       </c>
       <c r="G98" s="28"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" s="57"/>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99" s="81"/>
       <c r="B99" s="28" t="s">
         <v>6</v>
       </c>
@@ -3503,8 +4164,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" s="57"/>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100" s="81"/>
       <c r="B100" s="28" t="s">
         <v>6</v>
       </c>
@@ -3522,8 +4183,8 @@
       </c>
       <c r="G100" s="28"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" s="57"/>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101" s="81"/>
       <c r="B101" s="28" t="s">
         <v>6</v>
       </c>
@@ -3541,8 +4202,8 @@
       </c>
       <c r="G101" s="28"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="57"/>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102" s="81"/>
       <c r="B102" s="37" t="s">
         <v>6</v>
       </c>
@@ -3562,7 +4223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5"/>
       <c r="B103" s="13"/>
       <c r="C103" s="6"/>
@@ -3571,8 +4232,8 @@
       <c r="F103" s="6"/>
       <c r="G103" s="7"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" s="53" t="s">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104" s="77" t="s">
         <v>100</v>
       </c>
       <c r="B104" s="28" t="s">
@@ -3594,8 +4255,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="54"/>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105" s="78"/>
       <c r="B105" s="28" t="s">
         <v>99</v>
       </c>
@@ -3615,8 +4276,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="54"/>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" s="78"/>
       <c r="B106" s="28" t="s">
         <v>99</v>
       </c>
@@ -3636,8 +4297,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="54"/>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107" s="78"/>
       <c r="B107" s="28" t="s">
         <v>99</v>
       </c>
@@ -3657,8 +4318,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="55"/>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108" s="79"/>
       <c r="B108" s="28" t="s">
         <v>99</v>
       </c>
@@ -3678,7 +4339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5"/>
       <c r="B109" s="13"/>
       <c r="C109" s="6"/>
@@ -3687,8 +4348,8 @@
       <c r="F109" s="6"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="56" t="s">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110" s="80" t="s">
         <v>103</v>
       </c>
       <c r="B110" s="28" t="s">
@@ -3710,8 +4371,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111" s="56"/>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111" s="80"/>
       <c r="B111" s="28" t="s">
         <v>101</v>
       </c>
@@ -3731,8 +4392,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112" s="56"/>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112" s="80"/>
       <c r="B112" s="28" t="s">
         <v>102</v>
       </c>
@@ -3752,8 +4413,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="56"/>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" s="80"/>
       <c r="B113" s="28" t="s">
         <v>102</v>
       </c>
@@ -3773,8 +4434,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="56"/>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" s="80"/>
       <c r="B114" s="28" t="s">
         <v>102</v>
       </c>
@@ -3794,8 +4455,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="56"/>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" s="80"/>
       <c r="B115" s="28" t="s">
         <v>101</v>
       </c>
@@ -3815,8 +4476,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="56"/>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" s="80"/>
       <c r="B116" s="28" t="s">
         <v>102</v>
       </c>
@@ -3836,8 +4497,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="56"/>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" s="80"/>
       <c r="B117" s="28" t="s">
         <v>102</v>
       </c>
@@ -3855,8 +4516,8 @@
       </c>
       <c r="G117" s="28"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="53"/>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" s="77"/>
       <c r="B118" s="28" t="s">
         <v>102</v>
       </c>
@@ -3874,7 +4535,7 @@
       </c>
       <c r="G118" s="28"/>
     </row>
-    <row r="119" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5"/>
       <c r="B119" s="13"/>
       <c r="C119" s="6"/>
@@ -3883,8 +4544,8 @@
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="53" t="s">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" s="77" t="s">
         <v>113</v>
       </c>
       <c r="B120" s="28" t="s">
@@ -3906,8 +4567,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="54"/>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" s="78"/>
       <c r="B121" s="28" t="s">
         <v>106</v>
       </c>
@@ -3927,8 +4588,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="54"/>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" s="78"/>
       <c r="B122" s="28" t="s">
         <v>107</v>
       </c>
@@ -3948,8 +4609,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="54"/>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" s="78"/>
       <c r="B123" s="28" t="s">
         <v>108</v>
       </c>
@@ -3967,8 +4628,8 @@
       </c>
       <c r="G123" s="28"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="54"/>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="78"/>
       <c r="B124" s="28" t="s">
         <v>109</v>
       </c>
@@ -3988,8 +4649,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="54"/>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="78"/>
       <c r="B125" s="28" t="s">
         <v>107</v>
       </c>
@@ -4009,8 +4670,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="54"/>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" s="78"/>
       <c r="B126" s="28" t="s">
         <v>106</v>
       </c>
@@ -4028,8 +4689,8 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="54"/>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" s="78"/>
       <c r="B127" s="28" t="s">
         <v>105</v>
       </c>
@@ -4047,8 +4708,8 @@
       </c>
       <c r="G127" s="28"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="54"/>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128" s="78"/>
       <c r="B128" s="28" t="s">
         <v>107</v>
       </c>
@@ -4066,8 +4727,8 @@
       </c>
       <c r="G128" s="28"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="54"/>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="78"/>
       <c r="B129" s="28" t="s">
         <v>110</v>
       </c>
@@ -4087,8 +4748,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="54"/>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="78"/>
       <c r="B130" s="28" t="s">
         <v>110</v>
       </c>
@@ -4108,8 +4769,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="54"/>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" s="78"/>
       <c r="B131" s="28" t="s">
         <v>105</v>
       </c>
@@ -4129,8 +4790,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="54"/>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="78"/>
       <c r="B132" s="28" t="s">
         <v>111</v>
       </c>
@@ -4150,8 +4811,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133" s="55"/>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="79"/>
       <c r="B133" s="28" t="s">
         <v>107</v>
       </c>
@@ -4171,7 +4832,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="3.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5"/>
       <c r="B134" s="13"/>
       <c r="C134" s="6"/>
@@ -4180,8 +4841,8 @@
       <c r="F134" s="6"/>
       <c r="G134" s="7"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135" s="56" t="s">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="80" t="s">
         <v>75</v>
       </c>
       <c r="B135" s="28" t="s">
@@ -4203,8 +4864,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136" s="56"/>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="80"/>
       <c r="B136" s="28" t="s">
         <v>118</v>
       </c>
@@ -4222,8 +4883,8 @@
       </c>
       <c r="G136" s="28"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="56"/>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="80"/>
       <c r="B137" s="28" t="s">
         <v>107</v>
       </c>
@@ -4243,8 +4904,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138" s="56"/>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="80"/>
       <c r="B138" s="28" t="s">
         <v>118</v>
       </c>
@@ -4264,8 +4925,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139" s="56"/>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="80"/>
       <c r="B139" s="28" t="s">
         <v>119</v>
       </c>
@@ -4285,8 +4946,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="56"/>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A140" s="80"/>
       <c r="B140" s="28" t="s">
         <v>120</v>
       </c>
@@ -4306,8 +4967,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="56"/>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141" s="80"/>
       <c r="B141" s="28" t="s">
         <v>121</v>
       </c>
@@ -4327,8 +4988,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="56"/>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A142" s="80"/>
       <c r="B142" s="28" t="s">
         <v>122</v>
       </c>
@@ -4348,8 +5009,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="56"/>
+    <row r="143" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="80"/>
       <c r="B143" s="28" t="s">
         <v>123</v>
       </c>
@@ -4367,7 +5028,7 @@
       </c>
       <c r="G143" s="28"/>
     </row>
-    <row r="144" spans="1:7" ht="3.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5"/>
       <c r="B144" s="13"/>
       <c r="C144" s="6"/>
@@ -4376,8 +5037,8 @@
       <c r="F144" s="6"/>
       <c r="G144" s="7"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A145" s="53" t="s">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A145" s="77" t="s">
         <v>134</v>
       </c>
       <c r="B145" s="28" t="s">
@@ -4399,8 +5060,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146" s="54"/>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A146" s="78"/>
       <c r="B146" s="28" t="s">
         <v>105</v>
       </c>
@@ -4420,8 +5081,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147" s="54"/>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A147" s="78"/>
       <c r="B147" s="28" t="s">
         <v>105</v>
       </c>
@@ -4441,8 +5102,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148" s="54"/>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A148" s="78"/>
       <c r="B148" s="28" t="s">
         <v>105</v>
       </c>
@@ -4460,8 +5121,8 @@
       </c>
       <c r="G148" s="28"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149" s="54"/>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A149" s="78"/>
       <c r="B149" s="28" t="s">
         <v>105</v>
       </c>
@@ -4479,8 +5140,8 @@
       </c>
       <c r="G149" s="28"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150" s="55"/>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A150" s="79"/>
       <c r="B150" s="28" t="s">
         <v>105</v>
       </c>
@@ -4500,7 +5161,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="3.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5"/>
       <c r="B151" s="13"/>
       <c r="C151" s="6"/>
@@ -4533,18 +5194,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34FC3BC-25B6-4D42-9501-B427D819CC23}">
   <dimension ref="A1:H72"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="31.87890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.05859375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5234375" style="36" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="29" customWidth="1"/>
-    <col min="6" max="6" width="13.98828125" style="29" customWidth="1"/>
-    <col min="7" max="7" width="11.97265625" customWidth="1"/>
-    <col min="8" max="8" width="14.66015625" customWidth="1"/>
+    <col min="2" max="2" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" style="36" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="14" style="29" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
@@ -4567,8 +5228,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+    <row r="2" spans="1:8" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
         <v>74</v>
       </c>
       <c r="B2" s="45" t="s">
@@ -4593,8 +5254,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="59"/>
+    <row r="3" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A3" s="83"/>
       <c r="B3" s="45" t="s">
         <v>65</v>
       </c>
@@ -4617,8 +5278,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="59"/>
+    <row r="4" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="83"/>
       <c r="B4" s="45" t="s">
         <v>65</v>
       </c>
@@ -4641,8 +5302,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="59"/>
+    <row r="5" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="83"/>
       <c r="B5" s="45"/>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -4651,8 +5312,8 @@
       <c r="G5" s="30"/>
       <c r="H5" s="32"/>
     </row>
-    <row r="6" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="59"/>
+    <row r="6" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="83"/>
       <c r="B6" s="45"/>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4661,8 +5322,8 @@
       <c r="G6" s="30"/>
       <c r="H6" s="32"/>
     </row>
-    <row r="7" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="59"/>
+    <row r="7" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="83"/>
       <c r="B7" s="45"/>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4671,8 +5332,8 @@
       <c r="G7" s="30"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="59"/>
+    <row r="8" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="83"/>
       <c r="B8" s="45"/>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
@@ -4681,8 +5342,8 @@
       <c r="G8" s="30"/>
       <c r="H8" s="32"/>
     </row>
-    <row r="9" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="59"/>
+    <row r="9" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="83"/>
       <c r="B9" s="45"/>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4691,8 +5352,8 @@
       <c r="G9" s="30"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="59"/>
+    <row r="10" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="83"/>
       <c r="B10" s="45"/>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4701,8 +5362,8 @@
       <c r="G10" s="30"/>
       <c r="H10" s="32"/>
     </row>
-    <row r="11" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="59"/>
+    <row r="11" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="83"/>
       <c r="B11" s="45"/>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4711,8 +5372,8 @@
       <c r="G11" s="30"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="59"/>
+    <row r="12" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="83"/>
       <c r="B12" s="45"/>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
@@ -4721,8 +5382,8 @@
       <c r="G12" s="30"/>
       <c r="H12" s="32"/>
     </row>
-    <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="59"/>
+    <row r="13" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="83"/>
       <c r="B13" s="45"/>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4731,8 +5392,8 @@
       <c r="G13" s="30"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="59"/>
+    <row r="14" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="83"/>
       <c r="B14" s="45"/>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4741,8 +5402,8 @@
       <c r="G14" s="30"/>
       <c r="H14" s="32"/>
     </row>
-    <row r="15" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="59"/>
+    <row r="15" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="83"/>
       <c r="B15" s="45"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -4751,8 +5412,8 @@
       <c r="G15" s="30"/>
       <c r="H15" s="32"/>
     </row>
-    <row r="16" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="59"/>
+    <row r="16" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="83"/>
       <c r="B16" s="45"/>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4761,8 +5422,8 @@
       <c r="G16" s="30"/>
       <c r="H16" s="32"/>
     </row>
-    <row r="17" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="59"/>
+    <row r="17" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="83"/>
       <c r="B17" s="45"/>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4771,8 +5432,8 @@
       <c r="G17" s="30"/>
       <c r="H17" s="32"/>
     </row>
-    <row r="18" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="59"/>
+    <row r="18" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="83"/>
       <c r="B18" s="45"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -4781,8 +5442,8 @@
       <c r="G18" s="30"/>
       <c r="H18" s="32"/>
     </row>
-    <row r="19" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="59"/>
+    <row r="19" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="83"/>
       <c r="B19" s="45"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
@@ -4791,8 +5452,8 @@
       <c r="G19" s="30"/>
       <c r="H19" s="32"/>
     </row>
-    <row r="20" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="59"/>
+    <row r="20" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="83"/>
       <c r="B20" s="45"/>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -4801,8 +5462,8 @@
       <c r="G20" s="30"/>
       <c r="H20" s="32"/>
     </row>
-    <row r="21" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="59"/>
+    <row r="21" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="83"/>
       <c r="B21" s="45"/>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
@@ -4811,8 +5472,8 @@
       <c r="G21" s="30"/>
       <c r="H21" s="32"/>
     </row>
-    <row r="22" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
+    <row r="22" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="83"/>
       <c r="B22" s="45"/>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
@@ -4821,8 +5482,8 @@
       <c r="G22" s="30"/>
       <c r="H22" s="32"/>
     </row>
-    <row r="23" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="59"/>
+    <row r="23" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="83"/>
       <c r="B23" s="45"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
@@ -4831,8 +5492,8 @@
       <c r="G23" s="30"/>
       <c r="H23" s="32"/>
     </row>
-    <row r="24" spans="1:8" ht="3.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
+    <row r="24" spans="1:8" ht="3.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="83"/>
       <c r="B24" s="45"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
@@ -4841,8 +5502,8 @@
       <c r="G24" s="31"/>
       <c r="H24" s="32"/>
     </row>
-    <row r="25" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="59"/>
+    <row r="25" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="83"/>
       <c r="B25" s="47"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -4851,8 +5512,8 @@
       <c r="G25" s="14"/>
       <c r="H25" s="32"/>
     </row>
-    <row r="26" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="59"/>
+    <row r="26" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="83"/>
       <c r="B26" s="47"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -4861,8 +5522,8 @@
       <c r="G26" s="14"/>
       <c r="H26" s="32"/>
     </row>
-    <row r="27" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="59"/>
+    <row r="27" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="83"/>
       <c r="B27" s="47"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -4871,8 +5532,8 @@
       <c r="G27" s="14"/>
       <c r="H27" s="32"/>
     </row>
-    <row r="28" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="59"/>
+    <row r="28" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="83"/>
       <c r="B28" s="47"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -4881,8 +5542,8 @@
       <c r="G28" s="14"/>
       <c r="H28" s="32"/>
     </row>
-    <row r="29" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="59"/>
+    <row r="29" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="83"/>
       <c r="B29" s="47"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -4891,8 +5552,8 @@
       <c r="G29" s="14"/>
       <c r="H29" s="32"/>
     </row>
-    <row r="30" spans="1:8" ht="18" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+    <row r="30" spans="1:8" ht="18" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="83"/>
       <c r="B30" s="47"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -4901,8 +5562,8 @@
       <c r="G30" s="14"/>
       <c r="H30" s="32"/>
     </row>
-    <row r="31" spans="1:8" ht="3.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
+    <row r="31" spans="1:8" ht="3.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="83"/>
       <c r="B31" s="45"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
@@ -4911,8 +5572,8 @@
       <c r="G31" s="31"/>
       <c r="H31" s="32"/>
     </row>
-    <row r="32" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="59"/>
+    <row r="32" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="83"/>
       <c r="B32" s="45"/>
       <c r="C32" s="30"/>
       <c r="D32" s="30"/>
@@ -4921,8 +5582,8 @@
       <c r="G32" s="30"/>
       <c r="H32" s="32"/>
     </row>
-    <row r="33" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="59"/>
+    <row r="33" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="83"/>
       <c r="B33" s="45"/>
       <c r="C33" s="30"/>
       <c r="D33" s="30"/>
@@ -4931,8 +5592,8 @@
       <c r="G33" s="30"/>
       <c r="H33" s="32"/>
     </row>
-    <row r="34" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="59"/>
+    <row r="34" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="83"/>
       <c r="B34" s="45"/>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
@@ -4941,8 +5602,8 @@
       <c r="G34" s="30"/>
       <c r="H34" s="32"/>
     </row>
-    <row r="35" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="59"/>
+    <row r="35" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="83"/>
       <c r="B35" s="45"/>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
@@ -4951,8 +5612,8 @@
       <c r="G35" s="30"/>
       <c r="H35" s="32"/>
     </row>
-    <row r="36" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="59"/>
+    <row r="36" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="83"/>
       <c r="B36" s="45"/>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
@@ -4961,8 +5622,8 @@
       <c r="G36" s="30"/>
       <c r="H36" s="32"/>
     </row>
-    <row r="37" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="59"/>
+    <row r="37" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="83"/>
       <c r="B37" s="45"/>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
@@ -4971,8 +5632,8 @@
       <c r="G37" s="30"/>
       <c r="H37" s="32"/>
     </row>
-    <row r="38" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="59"/>
+    <row r="38" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="83"/>
       <c r="B38" s="45"/>
       <c r="C38" s="30"/>
       <c r="D38" s="30"/>
@@ -4981,8 +5642,8 @@
       <c r="G38" s="30"/>
       <c r="H38" s="32"/>
     </row>
-    <row r="39" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="59"/>
+    <row r="39" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="83"/>
       <c r="B39" s="45"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
@@ -4991,8 +5652,8 @@
       <c r="G39" s="30"/>
       <c r="H39" s="32"/>
     </row>
-    <row r="40" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="59"/>
+    <row r="40" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="83"/>
       <c r="B40" s="45"/>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
@@ -5001,8 +5662,8 @@
       <c r="G40" s="30"/>
       <c r="H40" s="32"/>
     </row>
-    <row r="41" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="59"/>
+    <row r="41" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="83"/>
       <c r="B41" s="45"/>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
@@ -5011,8 +5672,8 @@
       <c r="G41" s="30"/>
       <c r="H41" s="32"/>
     </row>
-    <row r="42" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="59"/>
+    <row r="42" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="83"/>
       <c r="B42" s="45"/>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
@@ -5021,8 +5682,8 @@
       <c r="G42" s="30"/>
       <c r="H42" s="32"/>
     </row>
-    <row r="43" spans="1:8" ht="14.45" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="59"/>
+    <row r="43" spans="1:8" ht="14.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="83"/>
       <c r="B43" s="45"/>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
@@ -5031,8 +5692,8 @@
       <c r="G43" s="30"/>
       <c r="H43" s="32"/>
     </row>
-    <row r="44" spans="1:8" ht="3.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
+    <row r="44" spans="1:8" ht="3.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="83"/>
       <c r="B44" s="45"/>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
@@ -5041,8 +5702,8 @@
       <c r="G44" s="31"/>
       <c r="H44" s="32"/>
     </row>
-    <row r="45" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="59"/>
+    <row r="45" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="83"/>
       <c r="B45" s="45"/>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -5051,8 +5712,8 @@
       <c r="G45" s="30"/>
       <c r="H45" s="32"/>
     </row>
-    <row r="46" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="59"/>
+    <row r="46" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="83"/>
       <c r="B46" s="45"/>
       <c r="C46" s="30"/>
       <c r="D46" s="30"/>
@@ -5061,8 +5722,8 @@
       <c r="G46" s="30"/>
       <c r="H46" s="32"/>
     </row>
-    <row r="47" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="59"/>
+    <row r="47" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="83"/>
       <c r="B47" s="45"/>
       <c r="C47" s="30"/>
       <c r="D47" s="30"/>
@@ -5071,8 +5732,8 @@
       <c r="G47" s="30"/>
       <c r="H47" s="32"/>
     </row>
-    <row r="48" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="59"/>
+    <row r="48" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="83"/>
       <c r="B48" s="45"/>
       <c r="C48" s="30"/>
       <c r="D48" s="30"/>
@@ -5081,8 +5742,8 @@
       <c r="G48" s="30"/>
       <c r="H48" s="32"/>
     </row>
-    <row r="49" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="59"/>
+    <row r="49" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="83"/>
       <c r="B49" s="48"/>
       <c r="C49" s="33"/>
       <c r="D49" s="33"/>
@@ -5091,8 +5752,8 @@
       <c r="G49" s="33"/>
       <c r="H49" s="32"/>
     </row>
-    <row r="50" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="59"/>
+    <row r="50" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="83"/>
       <c r="B50" s="48"/>
       <c r="C50" s="33"/>
       <c r="D50" s="33"/>
@@ -5101,8 +5762,8 @@
       <c r="G50" s="33"/>
       <c r="H50" s="32"/>
     </row>
-    <row r="51" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="59"/>
+    <row r="51" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="83"/>
       <c r="B51" s="48"/>
       <c r="C51" s="33"/>
       <c r="D51" s="33"/>
@@ -5111,8 +5772,8 @@
       <c r="G51" s="33"/>
       <c r="H51" s="32"/>
     </row>
-    <row r="52" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="59"/>
+    <row r="52" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="83"/>
       <c r="B52" s="48"/>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -5121,8 +5782,8 @@
       <c r="G52" s="33"/>
       <c r="H52" s="32"/>
     </row>
-    <row r="53" spans="1:8" ht="3.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
+    <row r="53" spans="1:8" ht="3.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="83"/>
       <c r="B53" s="45"/>
       <c r="C53" s="31"/>
       <c r="D53" s="31"/>
@@ -5131,8 +5792,8 @@
       <c r="G53" s="31"/>
       <c r="H53" s="32"/>
     </row>
-    <row r="54" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59"/>
+    <row r="54" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="83"/>
       <c r="B54" s="48"/>
       <c r="C54" s="33"/>
       <c r="D54" s="33"/>
@@ -5141,8 +5802,8 @@
       <c r="G54" s="33"/>
       <c r="H54" s="32"/>
     </row>
-    <row r="55" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="59"/>
+    <row r="55" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="83"/>
       <c r="B55" s="48"/>
       <c r="C55" s="33"/>
       <c r="D55" s="33"/>
@@ -5151,8 +5812,8 @@
       <c r="G55" s="33"/>
       <c r="H55" s="32"/>
     </row>
-    <row r="56" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="59"/>
+    <row r="56" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="83"/>
       <c r="B56" s="48"/>
       <c r="C56" s="33"/>
       <c r="D56" s="33"/>
@@ -5161,8 +5822,8 @@
       <c r="G56" s="33"/>
       <c r="H56" s="32"/>
     </row>
-    <row r="57" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="59"/>
+    <row r="57" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="83"/>
       <c r="B57" s="48"/>
       <c r="C57" s="33"/>
       <c r="D57" s="33"/>
@@ -5171,8 +5832,8 @@
       <c r="G57" s="33"/>
       <c r="H57" s="32"/>
     </row>
-    <row r="58" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="59"/>
+    <row r="58" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="83"/>
       <c r="B58" s="49"/>
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
@@ -5181,8 +5842,8 @@
       <c r="G58" s="34"/>
       <c r="H58" s="32"/>
     </row>
-    <row r="59" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="59"/>
+    <row r="59" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="83"/>
       <c r="B59" s="46"/>
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
@@ -5191,8 +5852,8 @@
       <c r="G59" s="35"/>
       <c r="H59" s="32"/>
     </row>
-    <row r="60" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
-      <c r="A60" s="60"/>
+    <row r="60" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="84"/>
       <c r="B60" s="46" t="s">
         <v>129</v>
       </c>
@@ -5215,8 +5876,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="58" t="s">
+    <row r="61" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="85" t="s">
         <v>75</v>
       </c>
       <c r="B61" s="32" t="s">
@@ -5239,8 +5900,8 @@
       </c>
       <c r="H61" s="32"/>
     </row>
-    <row r="62" spans="1:8" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="59"/>
+    <row r="62" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="86"/>
       <c r="B62" s="32" t="s">
         <v>69</v>
       </c>
@@ -5261,8 +5922,8 @@
       </c>
       <c r="H62" s="32"/>
     </row>
-    <row r="63" spans="1:8" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="59"/>
+    <row r="63" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="86"/>
       <c r="B63" s="32" t="s">
         <v>70</v>
       </c>
@@ -5281,8 +5942,8 @@
       </c>
       <c r="H63" s="32"/>
     </row>
-    <row r="64" spans="1:8" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="60"/>
+    <row r="64" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="86"/>
       <c r="B64" s="32" t="s">
         <v>72</v>
       </c>
@@ -5301,7 +5962,29 @@
       </c>
       <c r="H64" s="32"/>
     </row>
-    <row r="68" spans="4:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="86"/>
+      <c r="B65" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F65" s="14">
+        <v>88</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="H65" s="32"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D68" s="43" t="s">
         <v>127</v>
       </c>
@@ -5312,7 +5995,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="69" spans="4:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D69" s="44" t="s">
         <v>137</v>
       </c>
@@ -5321,7 +6004,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="70" spans="4:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D70" s="44" t="s">
         <v>135</v>
       </c>
@@ -5332,7 +6015,7 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="71" spans="4:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D71" s="44" t="s">
         <v>135</v>
       </c>
@@ -5343,7 +6026,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="72" spans="4:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72"/>
@@ -5352,10 +6035,3193 @@
   <autoFilter ref="B1:G23" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:A60"/>
-    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="A61:A65"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB3F4D0-9617-4F31-A173-84955510BD37}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F2" s="53">
+        <v>115</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="53"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="87"/>
+      <c r="B3" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="53">
+        <v>115</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="53"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="87"/>
+      <c r="B4" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F4" s="53">
+        <v>110</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="53"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="87"/>
+      <c r="B5" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="54">
+        <v>70</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="55"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="87"/>
+      <c r="B6" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="53">
+        <v>110</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="56"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="87"/>
+      <c r="B7" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F7" s="53">
+        <v>90</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H7" s="56"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="87"/>
+      <c r="B8" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="53">
+        <v>90</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H8" s="56"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="87"/>
+      <c r="B9" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F9" s="53">
+        <v>90</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H9" s="56"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="87"/>
+      <c r="B10" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="53">
+        <v>90</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="56"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="87"/>
+      <c r="B11" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F11" s="53">
+        <v>90</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="56"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="87"/>
+      <c r="B12" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F12" s="53">
+        <v>85</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="87"/>
+      <c r="B13" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="53">
+        <v>85</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H13" s="56"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="87"/>
+      <c r="B14" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F14" s="53">
+        <v>55</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14" s="56"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="87"/>
+      <c r="B15" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F15" s="53">
+        <v>55</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="56"/>
+    </row>
+    <row r="16" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="88" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F17" s="53">
+        <v>128</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="53"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="89"/>
+      <c r="B18" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F18" s="53">
+        <v>128</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="53"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="89"/>
+      <c r="B19" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F19" s="53">
+        <v>128</v>
+      </c>
+      <c r="G19" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="53"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="89"/>
+      <c r="B20" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F20" s="53">
+        <v>128</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="55"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="89"/>
+      <c r="B21" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F21" s="53">
+        <v>128</v>
+      </c>
+      <c r="G21" s="64"/>
+      <c r="H21" s="56"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="89"/>
+      <c r="B22" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="53">
+        <v>128</v>
+      </c>
+      <c r="G22" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="56"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="89"/>
+      <c r="B23" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F23" s="53">
+        <v>200</v>
+      </c>
+      <c r="G23" s="64"/>
+      <c r="H23" s="56"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="89"/>
+      <c r="B24" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="53">
+        <v>180</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="56"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="89"/>
+      <c r="B25" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F25" s="53">
+        <v>120</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="56"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="89"/>
+      <c r="B26" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="53">
+        <v>85</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="56"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="89"/>
+      <c r="B27" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" s="62">
+        <v>1.6</v>
+      </c>
+      <c r="F27" s="62">
+        <v>120</v>
+      </c>
+      <c r="G27" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="89"/>
+      <c r="B28" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F28" s="53">
+        <v>112</v>
+      </c>
+      <c r="G28" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="56"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="89"/>
+      <c r="B29" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="53">
+        <v>176</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="56"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="89"/>
+      <c r="B30" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F30" s="53">
+        <v>352</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="56"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="89"/>
+      <c r="B31" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="53">
+        <v>176</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="53"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="89"/>
+      <c r="B32" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F32" s="53">
+        <v>80</v>
+      </c>
+      <c r="G32" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="53"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="89"/>
+      <c r="B33" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F33" s="53">
+        <v>176</v>
+      </c>
+      <c r="G33" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="53"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="89"/>
+      <c r="B34" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F34" s="53">
+        <v>176</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="55"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="90"/>
+      <c r="B35" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F35" s="53">
+        <v>128</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A17:A35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACBE8C2-3C7B-4EF8-9BE6-6D55E41BE8FD}">
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="39" x14ac:dyDescent="0.35">
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="91" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F2" s="53">
+        <v>128</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="91"/>
+      <c r="B3" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="53">
+        <v>180</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="57"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="91"/>
+      <c r="B4" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F4" s="53">
+        <v>180</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="57"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="91"/>
+      <c r="B5" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="54">
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="54">
+        <v>128</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="65"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="91"/>
+      <c r="B6" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="53">
+        <v>115</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="91"/>
+      <c r="B7" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F7" s="53">
+        <v>128</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="52"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="91"/>
+      <c r="B8" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F8" s="53">
+        <v>128</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="52"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="91"/>
+      <c r="B9" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F9" s="53">
+        <v>120</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="52"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="91"/>
+      <c r="B10" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="62">
+        <v>2.13</v>
+      </c>
+      <c r="F10" s="62">
+        <v>55</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="52"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="91"/>
+      <c r="B11" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F11" s="53">
+        <v>60</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="52"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="91"/>
+      <c r="B12" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F12" s="53">
+        <v>128</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="91"/>
+      <c r="B13" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="53">
+        <v>70</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="52"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="91"/>
+      <c r="B14" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F14" s="53">
+        <v>80</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="52"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="92" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F15" s="53">
+        <v>80</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="93"/>
+      <c r="B16" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="53">
+        <v>136</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="93"/>
+      <c r="B17" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F17" s="53">
+        <v>60</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="93"/>
+      <c r="B18" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F18" s="53">
+        <v>120</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="93"/>
+      <c r="B19" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="62">
+        <v>1.6</v>
+      </c>
+      <c r="F19" s="62">
+        <v>120</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="67"/>
+    </row>
+    <row r="20" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A20" s="93"/>
+      <c r="B20" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F20" s="53">
+        <v>104</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A21" s="93"/>
+      <c r="B21" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F21" s="53">
+        <v>104</v>
+      </c>
+      <c r="G21" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A22" s="93"/>
+      <c r="B22" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="53">
+        <v>128</v>
+      </c>
+      <c r="G22" s="53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="93"/>
+      <c r="B23" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F23" s="53">
+        <v>104</v>
+      </c>
+      <c r="G23" s="53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="93"/>
+      <c r="B24" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="53">
+        <v>120</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="93"/>
+      <c r="B25" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F25" s="53">
+        <v>128</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="93"/>
+      <c r="B26" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="53">
+        <v>180</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="93"/>
+      <c r="B27" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F27" s="53">
+        <v>104</v>
+      </c>
+      <c r="G27" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A28" s="93"/>
+      <c r="B28" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F28" s="53">
+        <v>72</v>
+      </c>
+      <c r="G28" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="93"/>
+      <c r="B29" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="53">
+        <v>120</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A30" s="93"/>
+      <c r="B30" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F30" s="53">
+        <v>104</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="93"/>
+      <c r="B31" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="53">
+        <v>120</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="93"/>
+      <c r="B32" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F32" s="53">
+        <v>120</v>
+      </c>
+      <c r="G32" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="93"/>
+      <c r="B33" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F33" s="62">
+        <v>120</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="93"/>
+      <c r="B34" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F34" s="53">
+        <v>128</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="67"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="93"/>
+      <c r="B35" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F35" s="53">
+        <v>120</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="68"/>
+    </row>
+    <row r="36" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="93"/>
+      <c r="B36" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F36" s="53">
+        <v>128</v>
+      </c>
+      <c r="G36" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="68"/>
+    </row>
+    <row r="37" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A37" s="93"/>
+      <c r="B37" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F37" s="53">
+        <v>112</v>
+      </c>
+      <c r="G37" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="H37" s="68"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="93"/>
+      <c r="B38" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F38" s="53">
+        <v>128</v>
+      </c>
+      <c r="G38" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="68"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="93"/>
+      <c r="B39" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F39" s="53">
+        <v>128</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="68"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="93"/>
+      <c r="B40" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F40" s="53">
+        <v>128</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="68"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="93"/>
+      <c r="B41" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F41" s="53">
+        <v>128</v>
+      </c>
+      <c r="G41" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" s="67"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="93"/>
+      <c r="B42" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F42" s="53">
+        <v>120</v>
+      </c>
+      <c r="G42" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="67"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="93"/>
+      <c r="B43" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F43" s="53">
+        <v>128</v>
+      </c>
+      <c r="G43" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="67"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A14"/>
+    <mergeCell ref="A15:A43"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1842F17B-4801-4D3E-B1C4-884A19A81376}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.54296875" customWidth="1"/>
+    <col min="2" max="7" width="16.6328125" customWidth="1"/>
+    <col min="8" max="8" width="27.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="88" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F2" s="53">
+        <v>128</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57"/>
+    </row>
+    <row r="3" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="89"/>
+      <c r="B3" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="53">
+        <v>120</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="57"/>
+    </row>
+    <row r="4" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="89"/>
+      <c r="B4" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F4" s="53">
+        <v>180</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="57"/>
+    </row>
+    <row r="5" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="89"/>
+      <c r="B5" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="54">
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="54">
+        <v>128</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="65"/>
+    </row>
+    <row r="6" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="89"/>
+      <c r="B6" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F6" s="53">
+        <v>128</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="89"/>
+      <c r="B7" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F7" s="53">
+        <v>55</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="52"/>
+    </row>
+    <row r="8" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="89"/>
+      <c r="B8" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="53">
+        <v>128</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="52"/>
+    </row>
+    <row r="9" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="89"/>
+      <c r="B9" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F9" s="53">
+        <v>115</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="52"/>
+    </row>
+    <row r="10" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="90"/>
+      <c r="B10" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="62">
+        <v>180</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="52"/>
+    </row>
+    <row r="11" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="88" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F11" s="53">
+        <v>120</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="52"/>
+    </row>
+    <row r="12" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="89"/>
+      <c r="B12" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F12" s="53">
+        <v>104</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" s="66"/>
+    </row>
+    <row r="13" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="89"/>
+      <c r="B13" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="53">
+        <v>120</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A14" s="89"/>
+      <c r="B14" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F14" s="51">
+        <v>104</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="32"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="89"/>
+      <c r="B15" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F15" s="51">
+        <v>120</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="32"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="89"/>
+      <c r="B16" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="51">
+        <v>120</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="32"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="89"/>
+      <c r="B17" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F17" s="51">
+        <v>104</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="H17" s="32"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="89"/>
+      <c r="B18" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F18" s="51">
+        <v>104</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="32"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="63" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED855FE-BBB3-4D38-8F3E-A7CCF438D6ED}">
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.54296875" customWidth="1"/>
+    <col min="2" max="6" width="16.6328125" customWidth="1"/>
+    <col min="7" max="7" width="26.90625" customWidth="1"/>
+    <col min="8" max="8" width="27.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F2" s="53">
+        <v>112</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57"/>
+    </row>
+    <row r="3" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="87"/>
+      <c r="B3" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F3" s="53">
+        <v>60</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="57"/>
+    </row>
+    <row r="4" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="87"/>
+      <c r="B4" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F4" s="53">
+        <v>60</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="87"/>
+      <c r="B5" s="58" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="54">
+        <v>2.13</v>
+      </c>
+      <c r="F5" s="54">
+        <v>112</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="H5" s="66"/>
+    </row>
+    <row r="6" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="87"/>
+      <c r="B6" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="53">
+        <v>70</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="66"/>
+    </row>
+    <row r="7" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="87"/>
+      <c r="B7" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F7" s="53">
+        <v>60</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="66"/>
+    </row>
+    <row r="8" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="87"/>
+      <c r="B8" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="53">
+        <v>112</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="66"/>
+    </row>
+    <row r="9" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="87"/>
+      <c r="B9" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F9" s="53">
+        <v>112</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="H9" s="66"/>
+    </row>
+    <row r="10" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="87"/>
+      <c r="B10" s="57" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="53">
+        <v>120</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="66"/>
+    </row>
+    <row r="11" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="87"/>
+      <c r="B11" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F11" s="53">
+        <v>104</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="87"/>
+      <c r="B12" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F12" s="53">
+        <v>120</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="66"/>
+    </row>
+    <row r="13" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="87"/>
+      <c r="B13" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="53">
+        <v>280</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="72"/>
+    </row>
+    <row r="14" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="87"/>
+      <c r="B14" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F14" s="53">
+        <v>170</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="73"/>
+    </row>
+    <row r="15" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="87"/>
+      <c r="B15" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F15" s="53">
+        <v>120</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="73"/>
+    </row>
+    <row r="16" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="87"/>
+      <c r="B16" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="62">
+        <v>85</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="73"/>
+    </row>
+    <row r="17" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="87"/>
+      <c r="B17" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F17" s="53">
+        <v>72</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="87"/>
+      <c r="B18" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F18" s="53">
+        <v>112</v>
+      </c>
+      <c r="G18" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="32"/>
+    </row>
+    <row r="19" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="87"/>
+      <c r="B19" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F19" s="53">
+        <v>80</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="32"/>
+    </row>
+    <row r="20" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87"/>
+      <c r="B20" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="53">
+        <v>1.6</v>
+      </c>
+      <c r="F20" s="53">
+        <v>72</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="32"/>
+    </row>
+    <row r="21" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="87"/>
+      <c r="B21" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F21" s="53">
+        <v>70</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="87"/>
+      <c r="B22" s="61" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="D22" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="62">
+        <v>85</v>
+      </c>
+      <c r="G22" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F23" s="53">
+        <v>120</v>
+      </c>
+      <c r="G23" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="53">
+        <v>120</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F25" s="53">
+        <v>120</v>
+      </c>
+      <c r="G25" s="64"/>
+      <c r="H25" s="68" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="53">
+        <v>170</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F27" s="53">
+        <v>120</v>
+      </c>
+      <c r="G27" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F28" s="53">
+        <v>120</v>
+      </c>
+      <c r="G28" s="53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="53">
+        <v>120</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F30" s="53">
+        <v>120</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="53">
+        <v>112</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="53">
+        <v>2.13</v>
+      </c>
+      <c r="F32" s="53">
+        <v>104</v>
+      </c>
+      <c r="G32" s="53" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F33" s="53">
+        <v>104</v>
+      </c>
+      <c r="G33" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F34" s="53">
+        <v>120</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F35" s="53">
+        <v>120</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F36" s="53">
+        <v>120</v>
+      </c>
+      <c r="G36" s="53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F37" s="62">
+        <v>120</v>
+      </c>
+      <c r="G37" s="62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="53">
+        <v>2.4</v>
+      </c>
+      <c r="F38" s="53">
+        <v>120</v>
+      </c>
+      <c r="G38" s="53" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="23" x14ac:dyDescent="0.35">
+      <c r="B39" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="64"/>
+      <c r="F39" s="53">
+        <v>104</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="H39" s="67" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="23" x14ac:dyDescent="0.35">
+      <c r="B40" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="E40" s="64"/>
+      <c r="F40" s="53">
+        <v>104</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="H40" s="67" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="23" x14ac:dyDescent="0.35">
+      <c r="B41" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41" s="64"/>
+      <c r="F41" s="53">
+        <v>104</v>
+      </c>
+      <c r="G41" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="H41" s="67" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="B42" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F42" s="53">
+        <v>120</v>
+      </c>
+      <c r="G42" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="68"/>
+    </row>
+    <row r="43" spans="2:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="B43" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="64">
+        <v>1.6</v>
+      </c>
+      <c r="F43" s="53">
+        <v>72</v>
+      </c>
+      <c r="G43" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="68"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F44" s="53">
+        <v>120</v>
+      </c>
+      <c r="G44" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="68"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F45" s="53">
+        <v>120</v>
+      </c>
+      <c r="G45" s="64"/>
+      <c r="H45" s="68" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F46" s="53">
+        <v>120</v>
+      </c>
+      <c r="G46" s="53" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="F47" s="53">
+        <v>120</v>
+      </c>
+      <c r="G47" s="53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5633,10 +9499,16 @@
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="6243e079-1a6b-44b4-8f99-10940b916ec5"/>
     <ds:schemaRef ds:uri="74a5a733-6ac6-4145-b03d-28c6d22eb065"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5645,11 +9517,9 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FC91263-0795-488A-8D0A-58DA3416EB25}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6243e079-1a6b-44b4-8f99-10940b916ec5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="74a5a733-6ac6-4145-b03d-28c6d22eb065"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>